--- a/FLORES DE ESTRADA/Noviembre/PRORRATEO Noviembre Estrada.xlsx
+++ b/FLORES DE ESTRADA/Noviembre/PRORRATEO Noviembre Estrada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7154721-6911-4BF3-9027-39BD1AE93122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B3CB9A-F8B0-4676-92DE-B4411C79C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -268,7 +268,10 @@
     <t xml:space="preserve">Antonella </t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/11  LIQUIDACION : OCTUBRE</t>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>EXPENSAS - VENCIMIENTO 14/12  LIQUIDACION : NOVIEMBRE</t>
   </si>
 </sst>
 </file>
@@ -715,7 +718,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -742,7 +744,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1102,22 +1105,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="71"/>
+      <c r="A1" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1150,13 +1153,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="67">
+      <c r="J4" s="66">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="68"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="67"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1284,7 +1287,7 @@
       <c r="F11" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="72">
         <f>F11</f>
         <v>68600.000000000015</v>
       </c>
@@ -1331,23 +1334,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>1086296.6053298286</v>
-      </c>
-      <c r="G12" s="62"/>
+        <v>1236350.7065988535</v>
+      </c>
+      <c r="G12" s="72"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>1086296.6053298286</v>
+        <v>1236350.7065988535</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>95594.101269024919</v>
+        <v>108798.86218069911</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>1181890.7065988535</v>
+        <v>1345149.5687795526</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1359,7 +1362,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>1236350.7065988535</v>
+        <v>1399609.5687795526</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1381,7 +1384,7 @@
       <c r="F13" s="5">
         <v>56000</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="72">
         <f>F13</f>
         <v>56000</v>
       </c>
@@ -1412,7 +1415,7 @@
         <f>K13+L13+M13</f>
         <v>56000</v>
       </c>
-      <c r="P13" s="65">
+      <c r="P13" s="64">
         <f>G13+G30</f>
         <v>72521</v>
       </c>
@@ -1436,7 +1439,7 @@
       <c r="F14" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G14" s="62">
+      <c r="G14" s="72">
         <f t="shared" ref="G14" si="2">F14</f>
         <v>68600.000000000015</v>
       </c>
@@ -1472,10 +1475,10 @@
       <c r="A15" s="11">
         <v>5</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="63" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="55" t="s">
@@ -1487,7 +1490,7 @@
       <c r="F15" s="5">
         <v>54460</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="72">
         <f>F15</f>
         <v>54460</v>
       </c>
@@ -1535,25 +1538,23 @@
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>119609.0119221248</v>
-      </c>
-      <c r="G16" s="62">
-        <v>56000</v>
-      </c>
+        <v>125206.60497127178</v>
+      </c>
+      <c r="G16" s="72"/>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>63609.011922124802</v>
+        <v>125206.60497127178</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>5597.5930491469835</v>
+        <v>11018.181237471917</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>69206.60497127178</v>
+        <v>136224.7862087437</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1565,7 +1566,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>125206.60497127178</v>
+        <v>192224.7862087437</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1587,7 +1588,7 @@
       <c r="F17" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="72">
         <f t="shared" ref="G17:G21" si="4">F17</f>
         <v>68600.000000000015</v>
       </c>
@@ -1636,7 +1637,7 @@
       <c r="F18" s="5">
         <v>54460</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G18" s="72">
         <f t="shared" si="4"/>
         <v>54460</v>
       </c>
@@ -1687,7 +1688,7 @@
       <c r="F19" s="5">
         <v>56000</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="72">
         <f t="shared" si="4"/>
         <v>56000</v>
       </c>
@@ -1736,7 +1737,7 @@
       <c r="F20" s="5">
         <v>177240</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="72">
         <f>F20</f>
         <v>177240</v>
       </c>
@@ -1834,23 +1835,23 @@
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>105140</v>
-      </c>
-      <c r="G22" s="62"/>
+        <v>219532.32</v>
+      </c>
+      <c r="G22" s="72"/>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>105140</v>
+        <v>219532.32</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>9252.3200000000015</v>
+        <v>19318.844160000004</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>114392.32000000001</v>
+        <v>238851.16416000001</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
@@ -1862,7 +1863,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>219532.32</v>
+        <v>343991.16416000004</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1880,23 +1881,26 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>307569.36428821005</v>
-      </c>
-      <c r="G23" s="62"/>
+        <v>396935.46834557253</v>
+      </c>
+      <c r="G23" s="72">
+        <f>200000-63932</f>
+        <v>136068</v>
+      </c>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>307569.36428821005</v>
+        <v>260867.46834557253</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>27066.104057362489</v>
+        <v>22956.337214410385</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>334635.46834557253</v>
+        <v>283823.80555998289</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>396935.46834557253</v>
+        <v>346123.80555998289</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1928,7 +1932,7 @@
       <c r="F24" s="5">
         <v>86380</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="72">
         <f>F24</f>
         <v>86380</v>
       </c>
@@ -1977,25 +1981,25 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>534946.64633273333</v>
-      </c>
-      <c r="G25" s="62">
+        <v>576539.46321001393</v>
+      </c>
+      <c r="G25" s="72">
         <v>62301</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>472645.64633273333</v>
+        <v>514238.46321001393</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>41592.816877280537</v>
+        <v>45252.984762481232</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>514238.46321001387</v>
+        <v>559491.44797249511</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2007,7 +2011,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>576539.46321001393</v>
+        <v>621792.44797249511</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2027,26 +2031,26 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>1413768.5314904796</v>
-      </c>
-      <c r="G26" s="62">
-        <f>189300-110707</f>
-        <v>78593</v>
+        <v>1581331.9782616417</v>
+      </c>
+      <c r="G26" s="72">
+        <f>189300.5-110707</f>
+        <v>78593.5</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>1335175.5314904796</v>
+        <v>1502738.4782616417</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>117495.44677116221</v>
+        <v>132240.98608702447</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1452670.9782616417</v>
+        <v>1634979.4643486661</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2058,7 +2062,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1581331.9782616417</v>
+        <v>1763640.4643486661</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2080,7 +2084,7 @@
       <c r="F27" s="5">
         <v>16521</v>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="72">
         <f>F27</f>
         <v>16521</v>
       </c>
@@ -2127,23 +2131,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>157265.70583423419</v>
-      </c>
-      <c r="G28" s="62"/>
+        <v>187626.0879476468</v>
+      </c>
+      <c r="G28" s="72"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>157265.70583423419</v>
+        <v>187626.0879476468</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>13839.38211341261</v>
+        <v>16511.09573939292</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>171105.0879476468</v>
+        <v>204137.18368703971</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2155,7 +2159,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2173,23 +2177,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>157265.70583423419</v>
-      </c>
-      <c r="G29" s="62"/>
+        <v>187626.0879476468</v>
+      </c>
+      <c r="G29" s="72"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>157265.70583423419</v>
+        <v>187626.0879476468</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>13839.38211341261</v>
+        <v>16511.09573939292</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>171105.0879476468</v>
+        <v>204137.18368703971</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2201,7 +2205,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2221,7 +2225,7 @@
       <c r="F30" s="5">
         <v>16521</v>
       </c>
-      <c r="G30" s="62">
+      <c r="G30" s="72">
         <f>F30</f>
         <v>16521</v>
       </c>
@@ -2270,7 +2274,7 @@
       <c r="F31" s="5">
         <v>16521</v>
       </c>
-      <c r="G31" s="62">
+      <c r="G31" s="72">
         <f t="shared" ref="G31:G33" si="9">F31</f>
         <v>16521</v>
       </c>
@@ -2319,7 +2323,7 @@
       <c r="F32" s="5">
         <v>16521</v>
       </c>
-      <c r="G32" s="62">
+      <c r="G32" s="72">
         <f>F32</f>
         <v>16521</v>
       </c>
@@ -2359,7 +2363,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D33" s="55"/>
       <c r="E33" s="1">
@@ -2368,24 +2372,21 @@
       <c r="F33" s="5">
         <v>16521</v>
       </c>
-      <c r="G33" s="62">
-        <f t="shared" si="9"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="8">
+        <f t="shared" si="0"/>
         <v>16521</v>
-      </c>
-      <c r="H33" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1453.8480000000002</v>
       </c>
       <c r="K33" s="44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17974.848000000002</v>
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
@@ -2397,7 +2398,7 @@
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>16521</v>
+        <v>34495.847999999998</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2416,23 +2417,23 @@
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>16521</v>
-      </c>
-      <c r="G34" s="62"/>
+        <v>34495.847999999998</v>
+      </c>
+      <c r="G34" s="72"/>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>16521</v>
+        <v>34495.847999999998</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>1453.8480000000002</v>
+        <v>3035.6346240000003</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>17974.848000000002</v>
+        <v>37531.482623999997</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
@@ -2444,15 +2445,15 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>34495.847999999998</v>
+        <v>54052.482623999997</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2460,15 +2461,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>4779827.5710318442</v>
+        <v>5427089.5652826475</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1078339</v>
+        <v>1141886.5</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>3701488.5710318447</v>
+        <v>4285203.0652826475</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2476,7 +2477,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>325730.99425080232</v>
+        <v>377097.86974487297</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2489,7 +2490,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>5427089.5652826475</v>
+        <v>6062170.9350275202</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3265,11 +3266,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="72" t="s">
+      <c r="A29" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>
